--- a/강의예제/3장_보고서가_달라지는_서식_활용법/3장_종합문제.xlsx
+++ b/강의예제/3장_보고서가_달라지는_서식_활용법/3장_종합문제.xlsx
@@ -559,9 +559,9 @@
   ② 단위 접기         맨 뒤 쉼표로 천 단위 절삭                     (3-03)
   ③ 안내 문구 고치기  표 위 「(단위: 원)」 을 고칩니다               (3-03)
   ④ 0 감추기          0 을 하이픈으로 보이게                       (3-02)
-  ⑤ 달성률            J열 = 상반기합계 ÷ 목표, 0.0% 서식            (3-02)
+  ⑤ 달성률            K열 = 상반기 합계(J) ÷ 목표(I), 0.0% 서식     (3-02)
   ⑥ 줄 전체 강조      달성률 100% 미만인 줄 전체를 칠합니다          (3-04)
-  ⑦ 막대와 트렌드     I열에 데이터 막대, K열에 스파크라인            (3-05·3-07)
+  ⑦ 막대와 트렌드     J열에 데이터 막대, L열에 스파크라인            (3-05·3-07)
   ⑧ 최종확인 채우기   [최종확인] 다섯 칸                            —
 ■ 순서를 지켜야 하는 이유
   · ②를 하고 ③을 안 하면 **천 배 틀린 보고서**가 나갑니다.
@@ -1051,7 +1051,7 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>C6:I10 을 잡고 Ctrl+Shift+1. 또는 서식에 #,##0.</t>
+          <t>C6:J10 (월별 · 목표 · 합계) 을 잡고 Ctrl+Shift+1. 또는 서식에 #,##0.</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>J6 = I6/H6, 서식은 0.0%;[빨강]-0.0%;-;@ 입니다.</t>
+          <t>K6 = J6/I6 (합계 ÷ 목표) 을 넣고 K10 까지. 서식은 0.0%;[빨강]-0.0%;-;@ 입니다.</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>B6:J10 을 전부 잡고 새 규칙 → 수식 → =$J6&lt;1.</t>
+          <t>B6:K10 을 전부 잡고 새 규칙 → 수식 → =$K6&lt;1. $ 는 열 앞에만.</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>I6:I10 에 데이터 막대. K6 에 스파크라인(범위 C6:H6) 을 넣고 아래로 끕니다.</t>
+          <t>J6:J10(합계) 에 데이터 막대. L6 에 스파크라인(범위 C6:H6) 을 넣고 아래로 끕니다.</t>
         </is>
       </c>
     </row>
